--- a/GIS2/data_parcel.xlsx
+++ b/GIS2/data_parcel.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,7 +573,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2358/7</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>968</v>
+        <v>3273</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -601,7 +601,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>551 – podílové spoluvl. FO</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -614,35 +614,35 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-741549.62 -1049634.75 -741549.59 -1049628.21 -741549.98 -1049625.79 -741550.44 -1049623.38 -741550.97 -1049620.98 -741551.56 -1049618.6 -741552.22 -1049616.23 -741552.94 -1049613.88 -741553.73 -1049611.56 -741554.58 -1049609.25 -741555.49 -1049606.98 -741556.47 -1049604.72 -741557.51 -1049602.5 -741564.06 -1049589.82 -741574.55 -1049570.57 -741579.36 -1049562.46 -741589.25 -1049547.06 -741591.12 -1049544.88 -741591.88 -1049544.26 -741592.66 -1049543.69 -741593.49 -1049543.17 -741594.34 -1049542.69 -741595.21 -1049542.27 -741596.11 -1049541.89 -741597.32 -1049541.61 -741598.53 -1049541.4 -741599.76 -1049541.25 -741601 -1049541.16 -741602.23 -1049541.15 -741603.47 -1049541.2 -741604.7 -1049541.31 -741549.62 -1049634.75</t>
+          <t>-741875.18 -1049080.35 -741863.37 -1049075.33 -741861.15 -1049074.86 -741850.08 -1049072.8 -741848.41 -1049072.52 -741851.95 -1049055.86 -741852.55 -1049053.03 -741885.52 -1049059.06 -741943.19 -1049069.61 -741956.12 -1049071.86 -741969.45 -1049074.28 -741990.17 -1049077.93 -741995.34 -1049074.97 -741994.24 -1049084.79 -741994.26 -1049100.99 -741982.15 -1049095.59 -741966.16 -1049090.36 -741945.35 -1049087.15 -741939.06 -1049091.44 -741936.63 -1049097.06 -741934.5 -1049098.69 -741900.63 -1049090.94 -741901.67 -1049085.6 -741875.18 -1049080.35</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>ostatní plocha – zeleň</t>
+          <t>ostatní plocha</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>50.03039919</v>
+        <v>50.03448554</v>
       </c>
       <c r="T2" t="n">
-        <v>14.45083572</v>
+        <v>14.44502529</v>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2218251101</t>
+          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2214603101</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2358/10</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1334</v>
+        <v>9468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>551 – podílové spoluvl. FO</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -683,48 +683,48 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-741488.63 -1049738.17 -741482.6 -1049678.2 -741526.64 -1049673.72 -741488.63 -1049738.17</t>
+          <t>-741924.53 -1048855.76 -741959.53 -1048859.38 -741960.57 -1048859.06 -741963.52 -1048859.59 -741968.44 -1048860.48 -741969.43 -1048861.19 -741984.59 -1048862.86 -741977.08 -1048863.87 -741975.49 -1048864.99 -741972.19 -1048867.61 -741972.15 -1048869.44 -741976.57 -1048878.66 -741985.47 -1048894.11 -741988.84 -1048900.17 -741995.36 -1048911.87 -741999.08 -1048918.55 -742007.7 -1048935.05 -742014.04 -1048953 -742016.3 -1048952.17 -742018.76 -1048959.13 -742016.41 -1048959.94 -742017.2 -1048963.11 -742018.63 -1048970.36 -742018.14 -1048974.44 -742019.24 -1048978.24 -742023.54 -1048987.22 -742027.37 -1048988.19 -742033.62 -1048988.41 -742049.29 -1048996.24 -742060.71 -1049001.19 -742060.04 -1049002.29 -742055.71 -1049002.73 -742055.15 -1049002.8 -742052.26 -1049006.12 -742047.54 -1049008.89 -742031 -1049037.52 -742027.16 -1049043.8 -742024.19 -1049049.4 -742023.2 -1049050.5 -742024.15 -1049063.72 -742025.14 -1049083.08 -742025.83 -1049097.94 -742018.58 -1049111.85 -742017.65 -1049113.31 -742017.23 -1049114.24 -742017.68 -1049121.43 -742018.21 -1049122.45 -742021.69 -1049134.26 -742021.24 -1049134.3 -742012.33 -1049135.15 -742007.56 -1049135.61 -742004.98 -1049135.43 -742003.9 -1049129.04 -742003.01 -1049124.59 -741997.41 -1049119.72 -741989.09 -1049115.4 -741990.47 -1049110.5 -741991.91 -1049108.41 -741994.26 -1049100.99 -741994.24 -1049084.79 -741995.34 -1049074.97 -741996.14 -1049071.73 -741996.94 -1049068.49 -741996.47 -1049062.1 -741995.92 -1049053.49 -741995.48 -1049046.53 -741992.7 -1049045.5 -741992.34 -1049037.89 -741992.2 -1049034.79 -741995.24 -1049034.58 -741997.42 -1049020 -741997.36 -1049017.55 -741997.09 -1049006.5 -741996.84 -1049004.49 -741992.17 -1048978.23 -741991.04 -1048975.15 -741987.19 -1048964.6 -741984.02 -1048955.93 -741983.27 -1048956.16 -741973.78 -1048935.52 -741971.57 -1048931.1 -741958.58 -1048908.57 -741941.97 -1048878.9 -741932.41 -1048865.67 -741928.06 -1048862.59 -741925.31 -1048859.81 -741924.53 -1048855.76</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>ostatní plocha – zeleň</t>
+          <t>ostatní plocha</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>50.02952349</v>
+        <v>50.03505324</v>
       </c>
       <c r="T3" t="n">
-        <v>14.45200322</v>
+        <v>14.44361954</v>
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2436471101</t>
+          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2220332101</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2581/1</t>
+          <t>3320/15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nezjištěno</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29716</v>
+        <v>638</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nezjištěno</t>
+          <t>SV-I</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -737,63 +737,79 @@
           <t>Krč</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>V-22684/2023-101</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>551 – podílové spoluvl. FO</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>lv</t>
         </is>
+      </c>
+      <c r="L4" t="n">
+        <v>15949022</v>
+      </c>
+      <c r="M4" t="n">
+        <v>7299.32356979405</v>
       </c>
       <c r="O4" t="b">
         <v>0</v>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>27.04.2023</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-741284.02 -1049511.58 -741279.66 -1049511.21 -741284.95 -1049510.37 -741298.37 -1049509.1 -741358.47 -1049500.05 -741360.79 -1049499.7 -741369.94 -1049574.53 -741370.71 -1049581.12 -741379.34 -1049580.12 -741381.57 -1049599.7 -741380.54 -1049601.09 -741379.56 -1049602.83 -741379.23 -1049605.06 -741386.17 -1049662.61 -741388.56 -1049662.31 -741391.35 -1049687.2 -741482.6 -1049678.2 -741488.63 -1049738.17 -741460.37 -1049786.1 -741317.71 -1049750 -741316.3 -1049748.16 -741314.94 -1049746.28 -741313.65 -1049744.36 -741312.43 -1049742.39 -741311.27 -1049740.39 -741310.18 -1049738.34 -741309.16 -1049736.27 -741308.2 -1049734.16 -741307.32 -1049732.01 -741306.51 -1049729.84 -741305.77 -1049727.65 -741305.1 -1049725.43 -741304.51 -1049723.19 -741304 -1049720.93 -741303.56 -1049718.66 -741303.19 -1049716.37 -741302.14 -1049707.57 -741300.33 -1049691.2 -741301.44 -1049688.69 -741303.42 -1049687.5 -741309.49 -1049686.96 -741309.34 -1049682.12 -741305.64 -1049679.13 -741304.1 -1049666.88 -741303.96 -1049666 -741304.93 -1049666.15 -741298.91 -1049613.6 -741298.04 -1049613.44 -741297.02 -1049604.31 -741291 -1049594.26 -741283.04 -1049526.34 -741284.08 -1049524.31 -741285.68 -1049523.55 -741284.02 -1049511.58</t>
+          <t>-741982.01 -1049119.75 -741980.12 -1049129.29 -741927.14 -1049119.31 -741932.98 -1049107.93 -741932.66 -1049107.76 -741933.12 -1049106.97 -741933.48 -1049106.89 -741933.67 -1049106.54 -741933.57 -1049106.16 -741933.25 -1049106 -741933.5 -1049105.5 -741982.01 -1049119.75</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>ostatní plocha – jiná plocha</t>
+          <t>ostatní plocha</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>50.02997639</v>
+        <v>50.03411337</v>
       </c>
       <c r="T4" t="n">
-        <v>14.45400934</v>
+        <v>14.44462429</v>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2218606101</t>
+          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=71826971010</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2581/4</t>
+          <t>3320/16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nezjištěno</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11898</v>
+        <v>848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nezjištěno</t>
+          <t>SV-I</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -806,63 +822,79 @@
           <t>Krč</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>V-22684/2023-101</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>551 – podílové spoluvl. FO</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>lv</t>
         </is>
+      </c>
+      <c r="L5" t="n">
+        <v>15949022</v>
+      </c>
+      <c r="M5" t="n">
+        <v>7299.32356979405</v>
       </c>
       <c r="O5" t="b">
         <v>0</v>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>27.04.2023</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-741590.64 -1049729.7 -741571.09 -1049721.4 -741557.02 -1049777.7 -741580.44 -1049783.8 -741572.52 -1049825.84 -741539.25 -1049817.22 -741539.11 -1049815.81 -741531.67 -1049813.91 -741531.67 -1049815.36 -741508.13 -1049809.32 -741503.03 -1049808.01 -741490.86 -1049802.35 -741500.41 -1049764.01 -741500.95 -1049761.95 -741508.77 -1049742.53 -741525.58 -1049710.45 -741536.1 -1049692.39 -741549.34 -1049671.8 -741559.53 -1049656.74 -741564.97 -1049649.34 -741568.64 -1049644.53 -741581.99 -1049627.73 -741593.77 -1049613.98 -741603.96 -1049602.74 -741617.18 -1049588.87 -741590.64 -1049729.7</t>
+          <t>-741916.94 -1049117.29 -741808.26 -1049096.78 -741808.83 -1049093.8 -741810.84 -1049083.33 -741811.72 -1049083.41 -741839.44 -1049090.86 -741846.26 -1049092.69 -741845.68 -1049095.69 -741852.82 -1049097.12 -741852.13 -1049101.03 -741865.76 -1049103.6 -741866.39 -1049100.29 -741871.9 -1049101.29 -741874.78 -1049101.81 -741874.66 -1049102.44 -741892.91 -1049105.86 -741893.03 -1049105.27 -741894.37 -1049105.63 -741916.94 -1049117.29</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>ostatní plocha – jiná plocha</t>
+          <t>ostatní plocha</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>50.02935199</v>
+        <v>50.03445236</v>
       </c>
       <c r="T5" t="n">
-        <v>14.45125587</v>
+        <v>14.44625735</v>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2218608101</t>
+          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=71826972010</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2581/19</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nezjištěno</t>
+          <t>jiná plocha</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1971</v>
+        <v>699</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nezjištěno</t>
+          <t>SV-I</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -875,50 +907,66 @@
           <t>Krč</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>V-22684/2023-101</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>551 – podílové spoluvl. FO</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>lv</t>
         </is>
+      </c>
+      <c r="L6" t="n">
+        <v>15949022</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7299.32356979405</v>
       </c>
       <c r="O6" t="b">
         <v>0</v>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>27.04.2023</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-741454.19 -1049796.57 -741419.75 -1049792.47 -741416.27 -1049791.02 -741364.17 -1049777.7 -741361.85 -1049777.27 -741359.54 -1049776.76 -741357.25 -1049776.18 -741354.98 -1049775.53 -741352.73 -1049774.8 -741350.51 -1049774 -741348.31 -1049773.13 -741346.15 -1049772.19 -741344.01 -1049771.18 -741341.91 -1049770.09 -741339.85 -1049768.95 -741337.82 -1049767.73 -741335.84 -1049766.45 -741333.89 -1049765.11 -741332 -1049763.7 -741330.14 -1049762.24 -741328.34 -1049760.71 -741326.68 -1049759.32 -741325.07 -1049757.89 -741323.5 -1049756.4 -741321.98 -1049754.87 -741320.51 -1049753.29 -741319.08 -1049751.67 -741317.71 -1049750 -741460.37 -1049786.1 -741458.33 -1049789.56 -741454.19 -1049796.57</t>
+          <t>-741933.5 -1049105.5 -741933.25 -1049106 -741933.57 -1049106.16 -741933.67 -1049106.54 -741933.48 -1049106.89 -741933.12 -1049106.97 -741932.66 -1049107.76 -741932.98 -1049107.93 -741927.14 -1049119.31 -741916.94 -1049117.29 -741894.37 -1049105.63 -741893.03 -1049105.27 -741893.09 -1049104.96 -741897.91 -1049105.82 -741900.63 -1049090.94 -741934.5 -1049098.69 -741936.63 -1049097.06 -741935.86 -1049099.9 -741937.6 -1049100.39 -741936.51 -1049102.23 -741935.94 -1049101.63 -741935.73 -1049102.04 -741935.84 -1049102.42 -741935.6 -1049102.74 -741935.24 -1049102.83 -741934.93 -1049102.68 -741933.5 -1049105.5</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>ostatní plocha – jiná plocha</t>
+          <t>ostatní plocha</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>50.02895437</v>
+        <v>50.03429254</v>
       </c>
       <c r="T6" t="n">
-        <v>14.45378304</v>
+        <v>14.44518789</v>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2218620101</t>
+          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=3629263101</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2581/22</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -927,7 +975,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>812</v>
+        <v>800</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -946,7 +994,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>551 – podílové spoluvl. FO</t>
+          <t>7375</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -959,35 +1007,35 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-741593.01 -1049729.46 -741592.78 -1049730.59 -741590.64 -1049729.7 -741617.18 -1049588.87 -741623.73 -1049582.75 -741618.48 -1049610.97 -741611.47 -1049650.38 -741599.45 -1049715.35 -741593.58 -1049728.64 -741593.01 -1049729.46</t>
+          <t>-741901.67 -1049085.6 -741900.63 -1049090.94 -741897.91 -1049105.82 -741893.09 -1049104.96 -741893.03 -1049105.27 -741892.91 -1049105.86 -741874.66 -1049102.44 -741874.78 -1049101.81 -741871.9 -1049101.29 -741866.39 -1049100.29 -741865.76 -1049103.6 -741852.13 -1049101.03 -741852.82 -1049097.12 -741845.68 -1049095.69 -741846.26 -1049092.69 -741846.73 -1049090.14 -741857.92 -1049092.18 -741873.15 -1049094.96 -741873.41 -1049095.01 -741873.75 -1049093.36 -741872.97 -1049093.19 -741871.17 -1049092.8 -741872.88 -1049083.98 -741874.52 -1049084.26 -741875.18 -1049080.35 -741901.67 -1049085.6</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>zahrada</t>
+          <t>zastavěná plocha a nádvoří</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>50.02997833</v>
+        <v>50.03439988</v>
       </c>
       <c r="T7" t="n">
-        <v>14.45039183</v>
+        <v>14.44560124</v>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2218622101</t>
+          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2214602101</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2581/71</t>
+          <t>2/9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -996,7 +1044,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>155</v>
+        <v>224</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1015,7 +1063,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>551 – podílové spoluvl. FO</t>
+          <t>7375</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1028,35 +1076,35 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-741572.52 -1049825.84 -741580.44 -1049783.8 -741581.03 -1049783.94 -741585.61 -1049772.57 -741582.7 -1049804.01 -741578.78 -1049806.39 -741572.52 -1049825.84</t>
+          <t>-741874.52 -1049084.26 -741872.88 -1049083.98 -741871.17 -1049092.8 -741872.97 -1049093.19 -741873.75 -1049093.36 -741873.41 -1049095.01 -741873.15 -1049094.96 -741857.92 -1049092.18 -741861.15 -1049074.86 -741863.37 -1049075.33 -741875.18 -1049080.35 -741874.52 -1049084.26</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>zahrada</t>
+          <t>ostatní plocha</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>50.02858726</v>
+        <v>50.03450929</v>
       </c>
       <c r="T8" t="n">
-        <v>14.45111796</v>
+        <v>14.44585535</v>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2436473101</t>
+          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=3629262101</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2581/72</t>
+          <t>12/3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1065,7 +1113,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2083</v>
+        <v>423</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1084,7 +1132,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>551 – podílové spoluvl. FO</t>
+          <t>551</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1097,35 +1145,35 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-741617.18 -1049588.87 -741603.96 -1049602.74 -741593.77 -1049613.98 -741581.99 -1049627.73 -741568.64 -1049644.53 -741564.97 -1049649.34 -741559.53 -1049656.74 -741549.34 -1049671.8 -741536.1 -1049692.39 -741525.58 -1049710.45 -741508.77 -1049742.53 -741500.95 -1049761.95 -741500.41 -1049764.01 -741490.86 -1049802.35 -741503.03 -1049808.01 -741508.13 -1049809.32 -741507.55 -1049810.24 -741482.34 -1049806.89 -741474.97 -1049803.43 -741474.96 -1049800.24 -741521.43 -1049713.46 -741528.92 -1049699.48 -741537.12 -1049684.63 -741544.89 -1049671.84 -741546.34 -1049669.46 -741552.77 -1049658.42 -741560.52 -1049648.09 -741565.07 -1049641.72 -741577.93 -1049625.51 -741590.27 -1049609.49 -741599.61 -1049597.36 -741605.96 -1049586.39 -741607.34 -1049583.85 -741608.66 -1049581.27 -741609.9 -1049578.66 -741611.09 -1049576.02 -741612.2 -1049573.36 -741613.25 -1049570.66 -741613.72 -1049569.03 -741619.51 -1049541.39 -741620.26 -1049541.39 -741623.31 -1049541.99 -741623.35 -1049541.29 -741623.46 -1049540.6 -741623.63 -1049539.92 -741623.87 -1049539.26 -741624.17 -1049538.63 -741624.54 -1049538.03 -741624.95 -1049537.46 -741625.42 -1049536.94 -741625.94 -1049536.47 -741626.5 -1049536.05 -741626.96 -1049535.8 -741627.44 -1049535.62 -741627.95 -1049535.52 -741628.47 -1049535.5 -741628.98 -1049535.55 -741629.48 -1049535.68 -741629.96 -1049535.89 -741630.4 -1049536.16 -741630.79 -1049536.5 -741631.13 -1049536.89 -741631.4 -1049537.33 -741631.61 -1049537.8 -741631.74 -1049538.3 -741631.8 -1049538.82 -741629.04 -1049554.19 -741623.73 -1049582.75 -741617.18 -1049588.87</t>
+          <t>-741997.3 -1049124.24 -741982.01 -1049119.75 -741933.5 -1049105.5 -741934.93 -1049102.68 -741935.24 -1049102.83 -741935.6 -1049102.74 -741935.84 -1049102.42 -741935.73 -1049102.04 -741935.94 -1049101.63 -741936.51 -1049102.23 -741937.6 -1049100.39 -741952.23 -1049104.5 -741971.51 -1049109.89 -741989.09 -1049115.4 -741997.41 -1049119.72 -742003.01 -1049124.59 -742003.9 -1049129.04 -741997.3 -1049124.24</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>ostatní plocha – zeleň</t>
+          <t>ostatní plocha</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>50.03046037</v>
+        <v>50.03412938</v>
       </c>
       <c r="T9" t="n">
-        <v>14.45014375</v>
+        <v>14.44438755</v>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2436474101</t>
+          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2214612101</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2581/73</t>
+          <t>12/7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1134,7 +1182,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1481</v>
+        <v>889</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1153,7 +1201,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>551 – podílové spoluvl. FO</t>
+          <t>551</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1166,35 +1214,35 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>-741549.62 -1049634.75 -741604.7 -1049541.31 -741607.62 -1049542.96 -741608.17 -1049543.47 -741608.67 -1049544.03 -741609.1 -1049544.65 -741609.47 -1049545.3 -741609.76 -1049546 -741609.98 -1049546.71 -741610.13 -1049547.45 -741607.01 -1049566.86 -741603.97 -1049575.04 -741599.85 -1049582.67 -741592.91 -1049593.29 -741583.78 -1049605.54 -741556 -1049640.99 -741555.67 -1049641.34 -741555.3 -1049641.64 -741554.88 -1049641.88 -741554.43 -1049642.06 -741553.96 -1049642.17 -741553.49 -1049642.22 -741553.01 -1049642.19 -741552.54 -1049642.09 -741552.08 -1049641.93 -741551.66 -1049641.7 -741551.2 -1049641.38 -741550.8 -1049641 -741550.44 -1049640.56 -741550.14 -1049640.09 -741549.9 -1049639.58 -741549.74 -1049639.05 -741549.64 -1049638.5 -741549.62 -1049634.75</t>
+          <t>-741935.86 -1049099.9 -741936.63 -1049097.06 -741939.06 -1049091.44 -741945.35 -1049087.15 -741966.16 -1049090.36 -741982.15 -1049095.59 -741994.26 -1049100.99 -741991.91 -1049108.41 -741990.47 -1049110.5 -741989.09 -1049115.4 -741971.51 -1049109.89 -741952.23 -1049104.5 -741937.6 -1049100.39 -741935.86 -1049099.9</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>ostatní plocha – zeleň</t>
+          <t>ostatní plocha</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>50.03033588</v>
+        <v>50.03427177</v>
       </c>
       <c r="T10" t="n">
-        <v>14.45065647</v>
+        <v>14.44448711</v>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2436475101</t>
+          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2214616101</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2581/74</t>
+          <t>247/3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1203,7 +1251,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>79</v>
+        <v>2019</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1222,7 +1270,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>551 – podílové spoluvl. FO</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1235,35 +1283,35 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>-741542.07 -1049660.67 -741539.01 -1049663.27 -741535.87 -1049664.41 -741532.95 -1049664.76 -741531.86 -1049664.86 -741540.31 -1049650.53 -741542.06 -1049652.28 -741543.3 -1049656.38 -741543.33 -1049658.67 -741542.07 -1049660.67</t>
+          <t>-742045.03 -1049112.17 -742030.35 -1049102 -742025.83 -1049097.94 -742025.14 -1049083.08 -742024.15 -1049063.72 -742023.2 -1049050.5 -742024.19 -1049049.4 -742027.16 -1049043.8 -742031 -1049037.52 -742038.56 -1049041.72 -742042.93 -1049044.74 -742066.9 -1049059.81 -742065.77 -1049061.19 -742058.46 -1049070.17 -742055.44 -1049085.77 -742053.62 -1049095.32 -742052.68 -1049099.1 -742051.38 -1049112.11 -742046.27 -1049112.87 -742045.03 -1049112.17</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>ostatní plocha – zeleň</t>
+          <t>ostatní plocha</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>50.02983793</v>
+        <v>50.03437978</v>
       </c>
       <c r="T11" t="n">
-        <v>14.45144428</v>
+        <v>14.4433676</v>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2436476101</t>
+          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2214876101</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2581/75</t>
+          <t>12/1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1272,7 +1320,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>948</v>
+        <v>2300</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1291,7 +1339,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>551 – podílové spoluvl. FO</t>
+          <t>551</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1304,35 +1352,35 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>-741460.48 -1049797.32 -741454.19 -1049796.57 -741458.33 -1049789.56 -741460.37 -1049786.1 -741488.63 -1049738.17 -741526.64 -1049673.72 -741529.73 -1049668.49 -741530.3 -1049668.68 -741530.85 -1049668.93 -741531.36 -1049669.25 -741531.84 -1049669.63 -741532.26 -1049670.06 -741532.62 -1049670.55 -741532.93 -1049671.07 -741533.17 -1049671.62 -741533.34 -1049672.2 -741533.38 -1049673.02 -741533.44 -1049674.36 -741463.82 -1049793.55 -741460.48 -1049797.32</t>
+          <t>-741902.15 -1049051.63 -741891.23 -1049047.32 -741887.43 -1049055.14 -741880.38 -1049051.78 -741882 -1049048.2 -741883.93 -1049044.29 -741883.53 -1049044.09 -741885.12 -1049040.05 -741906.7 -1049040.97 -741924.59 -1049039.18 -741934.27 -1049034.78 -741992.34 -1049037.89 -741992.7 -1049045.5 -741983.49 -1049046.04 -741983.61 -1049051.56 -741979.36 -1049052.44 -741980.17 -1049057.01 -741988.49 -1049056.8 -741989.3 -1049061.8 -741996.47 -1049062.1 -741996.94 -1049068.49 -741996.14 -1049071.73 -741994.47 -1049072.07 -741902.15 -1049051.63</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>ostatní plocha – zeleň</t>
+          <t>ostatní plocha</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>50.02910407</v>
+        <v>50.03471383</v>
       </c>
       <c r="T12" t="n">
-        <v>14.45232007</v>
+        <v>14.4444808</v>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2436477101</t>
+          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2214610101</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2581/93</t>
+          <t>12/4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1341,7 +1389,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1538</v>
+        <v>956</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1360,7 +1408,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>551 – podílové spoluvl. FO</t>
+          <t>551</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1373,48 +1421,48 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-741462.65 -1049797.58 -741460.48 -1049797.32 -741463.82 -1049793.55 -741533.44 -1049674.36 -741533.38 -1049673.02 -741544.89 -1049671.84 -741537.12 -1049684.63 -741528.92 -1049699.48 -741521.43 -1049713.46 -741474.96 -1049800.24 -741474.97 -1049803.43 -741462.65 -1049797.58</t>
+          <t>-741996.14 -1049071.73 -741995.34 -1049074.97 -741990.17 -1049077.93 -741969.45 -1049074.28 -741956.12 -1049071.86 -741943.19 -1049069.61 -741885.52 -1049059.06 -741887.43 -1049055.14 -741891.23 -1049047.32 -741902.15 -1049051.63 -741994.47 -1049072.07 -741996.14 -1049071.73</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>ostatní plocha – jiná plocha</t>
+          <t>ostatní plocha</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>50.02937272</v>
+        <v>50.03465579</v>
       </c>
       <c r="T13" t="n">
-        <v>14.45186838</v>
+        <v>14.44498112</v>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2629873101</t>
+          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2214613101</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2581/70</t>
+          <t>12/6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>zahrada</t>
+          <t>Nezjištěno</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SV-G</t>
+          <t>Nezjištěno</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1427,197 +1475,43 @@
           <t>Krč</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>V-69710/2022-101</t>
-        </is>
-      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2059 – FO</t>
+          <t>551</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>lv</t>
         </is>
-      </c>
-      <c r="L14" t="n">
-        <v>90000</v>
-      </c>
-      <c r="M14" t="n">
-        <v>789.4736842105264</v>
       </c>
       <c r="O14" t="b">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>06.12.2022</t>
-        </is>
-      </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-741586.75 -1049760.18 -741585.61 -1049772.57 -741581.03 -1049783.94 -741580.44 -1049783.8 -741590.64 -1049729.7 -741592.78 -1049730.59 -741586.75 -1049760.18</t>
+          <t>-741995.48 -1049046.53 -741987.41 -1049047.02 -741987.83 -1049054.05 -741995.92 -1049053.49 -741996.47 -1049062.1 -741989.3 -1049061.8 -741988.49 -1049056.8 -741980.17 -1049057.01 -741979.36 -1049052.44 -741983.61 -1049051.56 -741983.49 -1049046.04 -741992.7 -1049045.5 -741995.48 -1049046.53</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>zahrada</t>
+          <t>ostatní plocha</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>50.02894484</v>
+        <v>50.03464832</v>
       </c>
       <c r="T14" t="n">
-        <v>14.45096614</v>
+        <v>14.44413617</v>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2436472101</t>
+          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2214615101</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>2581/2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Nezjištěno</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1285</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Nezjištěno</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Krč</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>1757 – HMP</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>lv</t>
-        </is>
-      </c>
-      <c r="O15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>-741590.64 -1049729.7 -741580.44 -1049783.8 -741557.02 -1049777.7 -741571.09 -1049721.4 -741590.64 -1049729.7</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>ostatní plocha – jiná plocha</t>
-        </is>
-      </c>
-      <c r="S15" t="n">
-        <v>50.028921</v>
-      </c>
-      <c r="T15" t="n">
-        <v>14.45111633</v>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2218607101</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>25.10.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2581/50</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Nezjištěno</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1364</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Nezjištěno</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Hlavní město Praha</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Krč</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>1757 – HMP</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>lv</t>
-        </is>
-      </c>
-      <c r="O16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>-741552.77 -1049658.42 -741546.34 -1049669.46 -741544.89 -1049671.84 -741533.38 -1049673.02 -741533.34 -1049672.2 -741533.17 -1049671.62 -741532.93 -1049671.07 -741532.62 -1049670.55 -741532.26 -1049670.06 -741531.84 -1049669.63 -741531.36 -1049669.25 -741530.85 -1049668.93 -741530.3 -1049668.68 -741529.73 -1049668.49 -741531.86 -1049664.86 -741532.95 -1049664.76 -741535.87 -1049664.41 -741539.01 -1049663.27 -741542.07 -1049660.67 -741543.33 -1049658.67 -741543.3 -1049656.38 -741542.06 -1049652.28 -741540.31 -1049650.53 -741549.62 -1049634.75 -741549.64 -1049638.5 -741549.74 -1049639.05 -741549.9 -1049639.58 -741550.14 -1049640.09 -741550.44 -1049640.56 -741550.8 -1049641 -741551.2 -1049641.38 -741551.66 -1049641.7 -741552.08 -1049641.93 -741552.54 -1049642.09 -741553.01 -1049642.19 -741553.49 -1049642.22 -741553.96 -1049642.17 -741554.43 -1049642.06 -741554.88 -1049641.88 -741555.3 -1049641.64 -741555.67 -1049641.34 -741556 -1049640.99 -741583.78 -1049605.54 -741592.91 -1049593.29 -741599.85 -1049582.67 -741603.97 -1049575.04 -741607.01 -1049566.86 -741610.13 -1049547.45 -741609.98 -1049546.71 -741609.76 -1049546 -741609.47 -1049545.3 -741609.1 -1049544.65 -741608.67 -1049544.03 -741608.17 -1049543.47 -741607.62 -1049542.96 -741604.7 -1049541.31 -741619.51 -1049541.39 -741613.72 -1049569.03 -741613.25 -1049570.66 -741612.2 -1049573.36 -741611.09 -1049576.02 -741609.9 -1049578.66 -741608.66 -1049581.27 -741607.34 -1049583.85 -741605.96 -1049586.39 -741599.61 -1049597.36 -741590.27 -1049609.49 -741577.93 -1049625.51 -741565.07 -1049641.72 -741560.52 -1049648.09 -741552.77 -1049658.42</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>ostatní plocha – jiná plocha</t>
-        </is>
-      </c>
-      <c r="S16" t="n">
-        <v>50.02986348</v>
-      </c>
-      <c r="T16" t="n">
-        <v>14.45123836</v>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>https://nahlizenidokn.cuzk.gov.cz/ZobrazObjekt.aspx?&amp;typ=parcela&amp;id=2218649101</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>25.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1543,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U16" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
